--- a/SFN/covariates/oafemScatter.xlsx
+++ b/SFN/covariates/oafemScatter.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avidachs/Documents/GitHub/rf1-sra-trust/SFN/Trust Behavioral Analysis/OAFEM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avidachs/Documents/GitHub/rf1-sra-trust/SFN/covariates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D146027-B594-3943-9110-14F4D619AF1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D725E0F2-D8E2-7A49-A289-374C45C69925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="980" windowWidth="24180" windowHeight="15620" xr2:uid="{06A61F8C-AD50-8240-932B-24E52E3BA800}"/>
   </bookViews>
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53375E68-07BE-624E-B3DA-934CD129D8BC}">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -1390,158 +1390,6 @@
         <v>62.91</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B72" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B73" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B74" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B75" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B76" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B77" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B78" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B79" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B80" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B81" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B82" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B83" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B84" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A85" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B85" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A86" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B86" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A87" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B87" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A88" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B88" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A89" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B89" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A90" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B90" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
